--- a/YoY_gross_tickets.xlsx
+++ b/YoY_gross_tickets.xlsx
@@ -455,8 +455,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -504,14 +504,14 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>9993612.699999999</v>
+        <v>8166817.2</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>8905512.699999999</v>
+        <v>6032571.9</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>-26.1%</t>
         </is>
       </c>
     </row>
@@ -522,14 +522,14 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>7394680</v>
+        <v>6479831.5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>5769615.3</v>
+        <v>5177123.633333334</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-20.1%</t>
         </is>
       </c>
     </row>
@@ -540,14 +540,14 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>5133113.6</v>
+        <v>3620281.766666667</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>36731592.8</v>
+        <v>12144832.3</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>+615.6%</t>
+          <t>+235.5%</t>
         </is>
       </c>
     </row>
@@ -558,14 +558,14 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>51808.3</v>
+        <v>48169.3</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>76726.39999999999</v>
+        <v>68648.89999999999</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>+48.1%</t>
+          <t>+42.5%</t>
         </is>
       </c>
     </row>
@@ -576,14 +576,14 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1272388.6</v>
+        <v>1124406.457142857</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1039305.3</v>
+        <v>766084.8</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-31.9%</t>
         </is>
       </c>
     </row>
@@ -594,14 +594,14 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>17208446.2</v>
+        <v>11229149.2</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17785187.5</v>
+        <v>10160542.16666667</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>+3.4%</t>
+          <t>-9.5%</t>
         </is>
       </c>
     </row>
@@ -612,14 +612,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>41054049.4</v>
+        <v>30668655.42380952</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>70307940</v>
+        <v>34349803.7</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>+71.3%</t>
+          <t>+12.0%</t>
         </is>
       </c>
     </row>
@@ -660,14 +660,14 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>10409311.9</v>
+        <v>8443096.4</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>9503454.800000001</v>
+        <v>6374926.3</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-24.5%</t>
         </is>
       </c>
     </row>
@@ -678,14 +678,14 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>7397709.4</v>
+        <v>6482860.9</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>5872869.8</v>
+        <v>5280378.133333334</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-18.5%</t>
         </is>
       </c>
     </row>
@@ -696,14 +696,14 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>8513430.199999999</v>
+        <v>4344482.7</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>36789562.3</v>
+        <v>12202801.8</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>+332.1%</t>
+          <t>+180.9%</t>
         </is>
       </c>
     </row>
@@ -714,14 +714,14 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>52648.9</v>
+        <v>49009.9</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>81847.8</v>
+        <v>73770.3</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>+55.5%</t>
+          <t>+50.5%</t>
         </is>
       </c>
     </row>
@@ -732,14 +732,14 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>1409704.6</v>
+        <v>1183655.6</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1103498.8</v>
+        <v>828696.8</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-30.0%</t>
         </is>
       </c>
     </row>
@@ -750,14 +750,14 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>19521817.7</v>
+        <v>11704022.2</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>18406572.7</v>
+        <v>10587724.86666667</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-9.5%</t>
         </is>
       </c>
     </row>
@@ -768,14 +768,14 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>47304622.7</v>
+        <v>32207127.7</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>71757806.19999999</v>
+        <v>35348298.2</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>+51.7%</t>
+          <t>+9.8%</t>
         </is>
       </c>
     </row>
@@ -794,8 +794,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -843,14 +843,14 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>1221525131.8</v>
+        <v>963631209.96</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>1073695232.46</v>
+        <v>658868893.7333333</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-31.6%</t>
         </is>
       </c>
     </row>
@@ -861,14 +861,14 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>529953876.25</v>
+        <v>465835842.77</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>452805366.31</v>
+        <v>384422431.8083333</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-17.5%</t>
         </is>
       </c>
     </row>
@@ -879,14 +879,14 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>640212619.71</v>
+        <v>464228306.9466667</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>6207127487.16</v>
+        <v>1917021297.585</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>+869.5%</t>
+          <t>+312.9%</t>
         </is>
       </c>
     </row>
@@ -897,14 +897,14 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>3397132.81</v>
+        <v>2650812.81</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3408545.5</v>
+        <v>3054480.25</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>+0.3%</t>
+          <t>+15.2%</t>
         </is>
       </c>
     </row>
@@ -915,14 +915,14 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>109958584.06</v>
+        <v>85790795.88333334</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>90549215.17</v>
+        <v>54209373.09</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-36.8%</t>
         </is>
       </c>
     </row>
@@ -933,14 +933,14 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>2836840502.13</v>
+        <v>1570179868.866667</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>2862318538.5</v>
+        <v>1426406024.446667</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>+0.9%</t>
+          <t>-9.2%</t>
         </is>
       </c>
     </row>
@@ -951,14 +951,14 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>5341887846.76</v>
+        <v>3552316837.236667</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>10689904385.1</v>
+        <v>4443982500.913334</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>+100.1%</t>
+          <t>+25.1%</t>
         </is>
       </c>
     </row>
@@ -999,14 +999,14 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1276945939.68</v>
+        <v>1000150160.675</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>1122186834.33</v>
+        <v>686435097.145</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-31.4%</t>
         </is>
       </c>
     </row>
@@ -1017,14 +1017,14 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>530166713.7</v>
+        <v>466048680.22</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>458377156.18</v>
+        <v>389994221.6783333</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>-13.5%</t>
+          <t>-16.3%</t>
         </is>
       </c>
     </row>
@@ -1035,14 +1035,14 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>1067336134.79</v>
+        <v>563795047.36</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>6212867986.43</v>
+        <v>1922761796.855</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>+482.1%</t>
+          <t>+241.0%</t>
         </is>
       </c>
     </row>
@@ -1053,14 +1053,14 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>3427584.06</v>
+        <v>2681264.06</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>3603761.47</v>
+        <v>3249696.22</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>+5.1%</t>
+          <t>+21.2%</t>
         </is>
       </c>
     </row>
@@ -1071,14 +1071,14 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>134233920.67</v>
+        <v>94396320.16</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>94690760.79000001</v>
+        <v>58149738.21</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>-29.5%</t>
+          <t>-38.4%</t>
         </is>
       </c>
     </row>
@@ -1089,14 +1089,14 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>3166856041.05</v>
+        <v>1629494055.085</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>2924710812.62</v>
+        <v>1472281047.631667</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-9.6%</t>
         </is>
       </c>
     </row>
@@ -1107,14 +1107,14 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>6178966333.950001</v>
+        <v>3756565527.56</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>10816437311.82</v>
+        <v>4532871597.74</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>+75.1%</t>
+          <t>+20.7%</t>
         </is>
       </c>
     </row>

--- a/YoY_gross_tickets.xlsx
+++ b/YoY_gross_tickets.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tickets" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gross" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LN Tickets" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LN Gross" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1121,4 +1123,682 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Live Nation Venues – Tickets Sold</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>LN Tickets Announced by Cutoff (2024 cutoff 2024-08-25; 2025 cutoff 2025-08-25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>% Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1030950.4</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1207688.166666667</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>+17.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>4397776.2</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3678071.366666667</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>-16.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>161356.4</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1621413</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>+904.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>47817.6</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>65148.8</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>+36.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>668387.5571428571</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>416914.8</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>-37.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>293625.2</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>597591.1333333333</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>+103.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>6599913.357142858</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>7586827.266666666</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>+15.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>LN Tickets – Full Year (No Cutoff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>% Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1044542.4</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1325749.633333333</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>+26.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>4398005.6</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>3759801.566666667</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>-14.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>161356.4</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1621413</v>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>+904.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>48658.2</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>70270.2</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>+44.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>696653.4</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>454167.9</v>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>-34.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>298000.7</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>605839.0333333333</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>+103.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>6647216.700000001</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>7837241.333333334</v>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>+17.9%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Live Nation Venues – Gross Sales (USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>LN Gross Announced by Cutoff (2024 cutoff 2024-08-25; 2025 cutoff 2025-08-25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>% Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>67017240.78</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>102789865.6216667</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>+53.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>294007559.32</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>232454738.945</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>-20.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>14870454.2</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>194816689.42</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>+1210.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>2641071.41</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>2908638.75</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>+10.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>47021909.45333333</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>23904371.72</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>-49.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>26919138.46</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>78172150.105</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>+190.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>452477373.6233333</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>635046454.5616667</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>+40.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>LN Gross – Full Year (No Cutoff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>% Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>68563242.78</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>111272152.9883333</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>+62.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>294013346.77</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>236701286.795</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>-19.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>14870454.2</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>194816689.42</v>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>+1210.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>2671522.66</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>3103854.72</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>+16.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>51194601.18</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>25897119.57</v>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>-49.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>27150096.05</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>78580620.985</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>+189.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>458463263.64</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>650371724.4783335</v>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>+41.9%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/YoY_gross_tickets.xlsx
+++ b/YoY_gross_tickets.xlsx
@@ -7,10 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tickets" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gross" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LN Tickets" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LN Gross" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All LN Annc (M + Est) Tix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All LN Annc (M + Est) Gross" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LN Matched Only (No Est) Tix" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LN Matched Only (No Est) Gross" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LN Owned-Op Venue (M + Est) Tix" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LN Owned-Op Venue (M + Est) Grs" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -465,7 +467,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Year-over-Year Comparison – Tickets Sold</t>
+          <t>All LN Announcements – Tickets Sold (Matched + Estimated)</t>
         </is>
       </c>
     </row>
@@ -473,7 +475,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Tickets Announced by Cutoff (2024 cutoff 2024-08-25; 2025 cutoff 2025-08-25)</t>
+          <t>Announced by Cutoff (2024 cutoff 2024-08-25; 2025 cutoff 2025-08-25)</t>
         </is>
       </c>
     </row>
@@ -506,14 +508,14 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>8166817.2</v>
+        <v>7742913.7</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>6032571.9</v>
+        <v>5474156.1</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-29.3%</t>
         </is>
       </c>
     </row>
@@ -524,14 +526,14 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>6479831.5</v>
+        <v>6121236.1</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>5177123.633333334</v>
+        <v>4964084.2</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-18.9%</t>
         </is>
       </c>
     </row>
@@ -542,14 +544,14 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>3620281.766666667</v>
+        <v>2663344.066666666</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>12144832.3</v>
+        <v>10782748.6</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>+235.5%</t>
+          <t>+304.9%</t>
         </is>
       </c>
     </row>
@@ -560,14 +562,14 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>48169.3</v>
+        <v>28406.6</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>68648.89999999999</v>
+        <v>38255.9</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>+42.5%</t>
+          <t>+34.7%</t>
         </is>
       </c>
     </row>
@@ -578,14 +580,14 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1124406.457142857</v>
+        <v>862925.8571428572</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>766084.8</v>
+        <v>828467.4</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-4.0%</t>
         </is>
       </c>
     </row>
@@ -596,14 +598,14 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>11229149.2</v>
+        <v>13249829.1</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>10160542.16666667</v>
+        <v>12262091.5</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-7.5%</t>
         </is>
       </c>
     </row>
@@ -629,7 +631,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Tickets – Full Year (No Cutoff)</t>
+          <t>Full Year (No Cutoff)</t>
         </is>
       </c>
     </row>
@@ -662,14 +664,14 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>8443096.4</v>
+        <v>8011164.4</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>6374926.3</v>
+        <v>5786210.7</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-27.8%</t>
         </is>
       </c>
     </row>
@@ -680,14 +682,14 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>6482860.9</v>
+        <v>6121236.1</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>5280378.133333334</v>
+        <v>5069181.3</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-17.2%</t>
         </is>
       </c>
     </row>
@@ -698,14 +700,14 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>4344482.7</v>
+        <v>3387545</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>12202801.8</v>
+        <v>10838752.4</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>+180.9%</t>
+          <t>+220.0%</t>
         </is>
       </c>
     </row>
@@ -716,14 +718,14 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>49009.9</v>
+        <v>28636</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>73770.3</v>
+        <v>39825.2</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>+50.5%</t>
+          <t>+39.1%</t>
         </is>
       </c>
     </row>
@@ -734,14 +736,14 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>1183655.6</v>
+        <v>927391.1</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>828696.8</v>
+        <v>898087.1</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-3.2%</t>
         </is>
       </c>
     </row>
@@ -752,14 +754,14 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>11704022.2</v>
+        <v>13731155.1</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>10587724.86666667</v>
+        <v>12716241.5</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-7.4%</t>
         </is>
       </c>
     </row>
@@ -797,14 +799,14 @@
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Year-over-Year Comparison – Gross Sales (USD)</t>
+          <t>All LN Announcements – Gross Sales USD (Matched + Estimated)</t>
         </is>
       </c>
     </row>
@@ -812,7 +814,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Gross Announced by Cutoff (2024 cutoff 2024-08-25; 2025 cutoff 2025-08-25)</t>
+          <t>Announced by Cutoff (2024 cutoff 2024-08-25; 2025 cutoff 2025-08-25)</t>
         </is>
       </c>
     </row>
@@ -845,14 +847,14 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>963631209.96</v>
+        <v>956966716.11</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>658868893.7333333</v>
+        <v>621512615.0983334</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-35.1%</t>
         </is>
       </c>
     </row>
@@ -863,14 +865,14 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>465835842.77</v>
+        <v>374029098.18</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>384422431.8083333</v>
+        <v>309199348.52</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-17.3%</t>
         </is>
       </c>
     </row>
@@ -881,14 +883,14 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>464228306.9466667</v>
+        <v>336738289.2466667</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>1917021297.585</v>
+        <v>1673799095.27</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>+312.9%</t>
+          <t>+397.1%</t>
         </is>
       </c>
     </row>
@@ -899,14 +901,14 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>2650812.81</v>
+        <v>1033187.87</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3054480.25</v>
+        <v>1417830.42</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>+15.2%</t>
+          <t>+37.2%</t>
         </is>
       </c>
     </row>
@@ -917,14 +919,14 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>85790795.88333334</v>
+        <v>66792551.59333333</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>54209373.09</v>
+        <v>68033408.40000001</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>-36.8%</t>
+          <t>+1.9%</t>
         </is>
       </c>
     </row>
@@ -935,14 +937,14 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1570179868.866667</v>
+        <v>1816756994.236667</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1426406024.446667</v>
+        <v>1770020203.205</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-2.6%</t>
         </is>
       </c>
     </row>
@@ -968,7 +970,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Gross – Full Year (No Cutoff)</t>
+          <t>Full Year (No Cutoff)</t>
         </is>
       </c>
     </row>
@@ -1001,14 +1003,14 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1000150160.675</v>
+        <v>992031798.325</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>686435097.145</v>
+        <v>646970850.65</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-34.8%</t>
         </is>
       </c>
     </row>
@@ -1019,14 +1021,14 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>466048680.22</v>
+        <v>374029098.18</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>389994221.6783333</v>
+        <v>314326178.29</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.0%</t>
         </is>
       </c>
     </row>
@@ -1037,14 +1039,14 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>563795047.36</v>
+        <v>436305029.66</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>1922761796.855</v>
+        <v>1679388519.61</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>+241.0%</t>
+          <t>+284.9%</t>
         </is>
       </c>
     </row>
@@ -1055,14 +1057,14 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>2681264.06</v>
+        <v>1038975.32</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>3249696.22</v>
+        <v>1464091.83</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>+21.2%</t>
+          <t>+40.9%</t>
         </is>
       </c>
     </row>
@@ -1073,14 +1075,14 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>94396320.16</v>
+        <v>75659484.70999999</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>58149738.21</v>
+        <v>72307195.77</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>-38.4%</t>
+          <t>-4.4%</t>
         </is>
       </c>
     </row>
@@ -1091,14 +1093,14 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1629494055.085</v>
+        <v>1877501141.365</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>1472281047.631667</v>
+        <v>1818414761.59</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-3.1%</t>
         </is>
       </c>
     </row>
@@ -1135,15 +1137,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Live Nation Venues – Tickets Sold</t>
+          <t>LN-Promoted Announcements Matched to a Reported Event – Tickets Sold (No Estimates)</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1153,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>LN Tickets Announced by Cutoff (2024 cutoff 2024-08-25; 2025 cutoff 2025-08-25)</t>
+          <t>Announced by Cutoff (2024 cutoff 2024-08-25; 2025 cutoff 2025-08-25)</t>
         </is>
       </c>
     </row>
@@ -1184,14 +1186,14 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1030950.4</v>
+        <v>6511796</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1207688.166666667</v>
+        <v>4423907.2</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>+17.1%</t>
+          <t>-32.1%</t>
         </is>
       </c>
     </row>
@@ -1202,14 +1204,14 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>4397776.2</v>
+        <v>5107195.5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>3678071.366666667</v>
+        <v>4042657.5</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-20.8%</t>
         </is>
       </c>
     </row>
@@ -1220,14 +1222,14 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>161356.4</v>
+        <v>1729234.166666667</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1621413</v>
+        <v>10187056</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>+904.9%</t>
+          <t>+489.1%</t>
         </is>
       </c>
     </row>
@@ -1238,14 +1240,14 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>47817.6</v>
+        <v>12595</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>65148.8</v>
+        <v>18817</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>+36.2%</t>
+          <t>+49.4%</t>
         </is>
       </c>
     </row>
@@ -1256,14 +1258,14 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>668387.5571428571</v>
+        <v>637312.8571428572</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>416914.8</v>
+        <v>525110</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-17.6%</t>
         </is>
       </c>
     </row>
@@ -1274,14 +1276,14 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>293625.2</v>
+        <v>11485657.5</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>597591.1333333333</v>
+        <v>10421450</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>+103.5%</t>
+          <t>-9.3%</t>
         </is>
       </c>
     </row>
@@ -1292,14 +1294,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>6599913.357142858</v>
+        <v>25483791.02380952</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>7586827.266666666</v>
+        <v>29618997.7</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>+15.0%</t>
+          <t>+16.2%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1309,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>LN Tickets – Full Year (No Cutoff)</t>
+          <t>Full Year (No Cutoff)</t>
         </is>
       </c>
     </row>
@@ -1340,14 +1342,14 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1044542.4</v>
+        <v>6751472.5</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1325749.633333333</v>
+        <v>4631354.5</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>+26.9%</t>
+          <t>-31.4%</t>
         </is>
       </c>
     </row>
@@ -1358,14 +1360,14 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>4398005.6</v>
+        <v>5107195.5</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>3759801.566666667</v>
+        <v>4042657.5</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-20.8%</t>
         </is>
       </c>
     </row>
@@ -1376,14 +1378,14 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>161356.4</v>
+        <v>2433677.5</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1621413</v>
+        <v>10187056</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>+904.9%</t>
+          <t>+318.6%</t>
         </is>
       </c>
     </row>
@@ -1394,14 +1396,14 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>48658.2</v>
+        <v>12595</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>70270.2</v>
+        <v>18817</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>+44.4%</t>
+          <t>+49.4%</t>
         </is>
       </c>
     </row>
@@ -1412,14 +1414,14 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>696653.4</v>
+        <v>693658</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>454167.9</v>
+        <v>555575.5</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>-34.8%</t>
+          <t>-19.9%</t>
         </is>
       </c>
     </row>
@@ -1430,14 +1432,14 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>298000.7</v>
+        <v>11949133.5</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>605839.0333333333</v>
+        <v>10615235.5</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>+103.3%</t>
+          <t>-11.2%</t>
         </is>
       </c>
     </row>
@@ -1448,14 +1450,14 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>6647216.700000001</v>
+        <v>26947732</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>7837241.333333334</v>
+        <v>30050696</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>+17.9%</t>
+          <t>+11.5%</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Live Nation Venues – Gross Sales (USD)</t>
+          <t>LN-Promoted Announcements Matched to a Reported Event – Gross Sales USD (No Estimates)</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1492,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>LN Gross Announced by Cutoff (2024 cutoff 2024-08-25; 2025 cutoff 2025-08-25)</t>
+          <t>Announced by Cutoff (2024 cutoff 2024-08-25; 2025 cutoff 2025-08-25)</t>
         </is>
       </c>
     </row>
@@ -1523,14 +1525,14 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>67017240.78</v>
+        <v>832500946.78</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>102789865.6216667</v>
+        <v>522216394.9983333</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>+53.4%</t>
+          <t>-37.3%</t>
         </is>
       </c>
     </row>
@@ -1541,14 +1543,14 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>294007559.32</v>
+        <v>318914244.23</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>232454738.945</v>
+        <v>263203806.85</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-17.5%</t>
         </is>
       </c>
     </row>
@@ -1559,14 +1561,14 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>14870454.2</v>
+        <v>213610561.2666667</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>194816689.42</v>
+        <v>1595705881.24</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>+1210.1%</t>
+          <t>+647.0%</t>
         </is>
       </c>
     </row>
@@ -1577,14 +1579,14 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>2641071.41</v>
+        <v>591829.5600000001</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2908638.75</v>
+        <v>781758.71</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>+10.1%</t>
+          <t>+32.1%</t>
         </is>
       </c>
     </row>
@@ -1595,14 +1597,14 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>47021909.45333333</v>
+        <v>52948392.76333334</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>23904371.72</v>
+        <v>44485758.95</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-16.0%</t>
         </is>
       </c>
     </row>
@@ -1613,14 +1615,14 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>26919138.46</v>
+        <v>1592511655.026667</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>78172150.105</v>
+        <v>1553051804.625</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>+190.4%</t>
+          <t>-2.5%</t>
         </is>
       </c>
     </row>
@@ -1631,14 +1633,14 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>452477373.6233333</v>
+        <v>3011077629.626667</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>635046454.5616667</v>
+        <v>3979445405.373333</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>+40.3%</t>
+          <t>+32.2%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1648,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>LN Gross – Full Year (No Cutoff)</t>
+          <t>Full Year (No Cutoff)</t>
         </is>
       </c>
     </row>
@@ -1679,14 +1681,14 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>68563242.78</v>
+        <v>864955216.655</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>111272152.9883333</v>
+        <v>538945276.64</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>+62.3%</t>
+          <t>-37.7%</t>
         </is>
       </c>
     </row>
@@ -1697,14 +1699,14 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>294013346.77</v>
+        <v>318914244.23</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>236701286.795</v>
+        <v>263203806.85</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-17.5%</t>
         </is>
       </c>
     </row>
@@ -1715,14 +1717,14 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>14870454.2</v>
+        <v>310249678.88</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>194816689.42</v>
+        <v>1595705881.24</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>+1210.1%</t>
+          <t>+414.3%</t>
         </is>
       </c>
     </row>
@@ -1733,14 +1735,14 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>2671522.66</v>
+        <v>591829.5600000001</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>3103854.72</v>
+        <v>781758.71</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>+16.2%</t>
+          <t>+32.1%</t>
         </is>
       </c>
     </row>
@@ -1751,14 +1753,14 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>51194601.18</v>
+        <v>61440496.38</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>25897119.57</v>
+        <v>46911681.49</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-23.6%</t>
         </is>
       </c>
     </row>
@@ -1769,14 +1771,14 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>27150096.05</v>
+        <v>1651753727.325</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>78580620.985</v>
+        <v>1573740756.28</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>+189.4%</t>
+          <t>-4.7%</t>
         </is>
       </c>
     </row>
@@ -1787,10 +1789,688 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
+        <v>3207905193.03</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>4019289161.21</v>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>+25.3%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LN Owned/Operated Venues – Tickets Sold (Matched + Estimated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Announced by Cutoff (2024 cutoff 2024-08-25; 2025 cutoff 2025-08-25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>% Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>793240.8</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>853597.5666666667</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>+7.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>5208795.8</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4400795.5</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>-15.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>161356.4</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1776579</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>+1001.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>28406.6</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>37422.8</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>+31.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>323765.7571428571</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>425620.8</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>+31.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>84348</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>92811.60000000001</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>+10.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>6599913.357142856</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>7586827.266666666</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>+15.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Full Year (No Cutoff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>% Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>806832.8</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>963960.2333333334</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>+19.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>5208795.8</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>4494674.4</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>-13.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>161356.4</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1776579</v>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>+1001.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>28636</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>38992.1</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>+36.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>357247.7</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>470224</v>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>+31.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>84348</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>92811.60000000001</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>+10.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>6647216.7</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>7837241.333333333</v>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>+17.9%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LN-Owned/Operated Venues – Gross Sales USD (Matched + Estimated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Announced by Cutoff (2024 cutoff 2024-08-25; 2025 cutoff 2025-08-25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>% Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>87554545.11</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>91045981.69666667</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>+4.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>313888112.47</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>270664834.5</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>-13.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>14870454.2</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>218008975.86</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>+1366.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>1033187.87</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>1382130.67</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>+33.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>23218502.43333333</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>34139999.54</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>+47.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>11912571.54</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>19804532.295</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>+66.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>452477373.6233334</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>635046454.5616665</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>+40.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Full Year (No Cutoff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>% Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>89100547.11</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>99570839.20333333</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>+11.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>313888112.47</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>275082705.74</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>-12.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>14870454.2</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>218008975.86</v>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>+1366.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>1038975.32</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>1428392.08</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>+37.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>27652603</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>36476279.3</v>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>+31.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>11912571.54</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>19804532.295</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>+66.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
         <v>458463263.64</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>650371724.4783335</v>
+        <v>650371724.4783332</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
